--- a/Team-Data/2013-14/1-18-2013-14.xlsx
+++ b/Team-Data/2013-14/1-18-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -775,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -796,22 +863,22 @@
         <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>26</v>
@@ -942,10 +1009,10 @@
         <v>18</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>25</v>
@@ -954,13 +1021,13 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
@@ -972,19 +1039,19 @@
         <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV3" t="n">
         <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1130,7 +1197,7 @@
         <v>16</v>
       </c>
       <c r="AM4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN4" t="n">
         <v>8</v>
@@ -1142,19 +1209,19 @@
         <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
@@ -1169,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
         <v>8</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
         <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.405</v>
+        <v>0.415</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
         <v>35</v>
       </c>
       <c r="J5" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.43</v>
+        <v>0.428</v>
       </c>
       <c r="L5" t="n">
         <v>5.4</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O5" t="n">
         <v>18.4</v>
@@ -1246,19 +1313,19 @@
         <v>25.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="S5" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T5" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="V5" t="n">
         <v>12.8</v>
@@ -1273,16 +1340,16 @@
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1291,13 +1358,13 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>28</v>
@@ -1315,13 +1382,13 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
         <v>26</v>
@@ -1330,22 +1397,22 @@
         <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>28</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.487</v>
+        <v>0.474</v>
       </c>
       <c r="H6" t="n">
         <v>48.9</v>
       </c>
       <c r="I6" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J6" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.426</v>
+        <v>0.424</v>
       </c>
       <c r="L6" t="n">
         <v>5.7</v>
       </c>
       <c r="M6" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O6" t="n">
         <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R6" t="n">
         <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="U6" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V6" t="n">
         <v>16.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
@@ -1512,19 +1579,19 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1722,7 @@
         <v>21</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
         <v>22</v>
@@ -1673,16 +1740,16 @@
         <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN7" t="n">
         <v>10</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>20</v>
@@ -1709,7 +1776,7 @@
         <v>22</v>
       </c>
       <c r="AX7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
@@ -1780,40 +1847,40 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N8" t="n">
         <v>0.381</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P8" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
         <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T8" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
@@ -1825,10 +1892,10 @@
         <v>18.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>104</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,7 +1904,7 @@
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1873,25 +1940,25 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
         <v>25</v>
       </c>
       <c r="AT8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1903,7 +1970,7 @@
         <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>11</v>
@@ -2040,10 +2107,10 @@
         <v>9</v>
       </c>
       <c r="AM9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2076,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
         <v>27</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -2117,34 +2184,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.425</v>
+        <v>0.41</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J10" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L10" t="n">
         <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N10" t="n">
         <v>0.31</v>
@@ -2153,13 +2220,13 @@
         <v>16.7</v>
       </c>
       <c r="P10" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.66</v>
+        <v>0.663</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="S10" t="n">
         <v>30.5</v>
@@ -2174,43 +2241,43 @@
         <v>15.5</v>
       </c>
       <c r="W10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="n">
         <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2222,7 +2289,7 @@
         <v>27</v>
       </c>
       <c r="AM10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2243,10 +2310,10 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV10" t="n">
         <v>23</v>
@@ -2258,10 +2325,10 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -2299,46 +2366,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.619</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J11" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L11" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M11" t="n">
         <v>24.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.387</v>
+        <v>0.39</v>
       </c>
       <c r="O11" t="n">
         <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="R11" t="n">
         <v>11.1</v>
@@ -2350,31 +2417,31 @@
         <v>46</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="V11" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
         <v>7.8</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
         <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.9</v>
+        <v>104</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2389,16 +2456,16 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
       </c>
       <c r="AK11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL11" t="n">
         <v>2</v>
@@ -2416,7 +2483,7 @@
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -2425,10 +2492,10 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>29</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
         <v>15</v>
@@ -2446,13 +2513,13 @@
         <v>25</v>
       </c>
       <c r="BA11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.643</v>
+        <v>0.634</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J12" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.472</v>
       </c>
       <c r="L12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M12" t="n">
         <v>25.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P12" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
@@ -2535,16 +2602,16 @@
         <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
         <v>20.4</v>
@@ -2553,10 +2620,10 @@
         <v>24.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.1</v>
+        <v>104.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2571,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,13 +2668,13 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>25</v>
@@ -2622,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.821</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
@@ -2681,7 +2748,7 @@
         <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.457</v>
@@ -2693,16 +2760,16 @@
         <v>19.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O13" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
         <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.791</v>
+        <v>0.787</v>
       </c>
       <c r="R13" t="n">
         <v>9.699999999999999</v>
@@ -2711,37 +2778,37 @@
         <v>34.9</v>
       </c>
       <c r="T13" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2762,16 +2829,16 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>21</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2780,10 +2847,10 @@
         <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
         <v>2</v>
@@ -2804,10 +2871,10 @@
         <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -2845,88 +2912,88 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
         <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J14" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O14" t="n">
         <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="R14" t="n">
         <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T14" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V14" t="n">
         <v>13.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA14" t="n">
         <v>23.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.6</v>
+        <v>106</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2935,16 +3002,16 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ14" t="n">
         <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2962,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -2977,16 +3044,16 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW14" t="n">
         <v>7</v>
       </c>
-      <c r="AW14" t="n">
-        <v>8</v>
-      </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ14" t="n">
         <v>21</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3178,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
         <v>22</v>
@@ -3126,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3141,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
         <v>18</v>
@@ -3156,7 +3223,7 @@
         <v>17</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3299,7 +3366,7 @@
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
@@ -3317,13 +3384,13 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>21</v>
@@ -3353,7 +3420,7 @@
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -3391,19 +3458,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.725</v>
+        <v>0.718</v>
       </c>
       <c r="H17" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I17" t="n">
         <v>38.9</v>
@@ -3421,34 +3488,34 @@
         <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O17" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>4.5</v>
@@ -3457,7 +3524,7 @@
         <v>3.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
         <v>21</v>
@@ -3466,10 +3533,10 @@
         <v>104</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3481,7 +3548,7 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
         <v>6</v>
@@ -3508,13 +3575,13 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3526,13 +3593,13 @@
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
         <v>21</v>
       </c>
       <c r="AY17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ17" t="n">
         <v>8</v>
@@ -3544,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -3573,85 +3640,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
-        <v>0.179</v>
+        <v>0.184</v>
       </c>
       <c r="H18" t="n">
         <v>48.9</v>
       </c>
       <c r="I18" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.421</v>
+        <v>0.419</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
         <v>20.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="O18" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
         <v>19.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="R18" t="n">
         <v>11.3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W18" t="n">
         <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
         <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
         <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3675,13 +3742,13 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,25 +3757,25 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
         <v>24</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3726,7 +3793,7 @@
         <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
         <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.475</v>
+        <v>0.462</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3773,7 +3840,7 @@
         <v>38.7</v>
       </c>
       <c r="J19" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="K19" t="n">
         <v>0.435</v>
@@ -3782,61 +3849,61 @@
         <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.346</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P19" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.782</v>
+        <v>0.789</v>
       </c>
       <c r="R19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="S19" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.4</v>
+        <v>106.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -3845,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>8</v>
@@ -3860,7 +3927,7 @@
         <v>15</v>
       </c>
       <c r="AM19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN19" t="n">
         <v>21</v>
@@ -3872,16 +3939,16 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -3890,7 +3957,7 @@
         <v>8</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3908,7 +3975,7 @@
         <v>2</v>
       </c>
       <c r="BC19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -3937,97 +4004,97 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.385</v>
+        <v>0.395</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="J20" t="n">
         <v>85.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M20" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.383</v>
+        <v>0.386</v>
       </c>
       <c r="O20" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0.765</v>
       </c>
       <c r="R20" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U20" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V20" t="n">
         <v>13.7</v>
       </c>
       <c r="W20" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X20" t="n">
         <v>6.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA20" t="n">
         <v>20.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI20" t="n">
         <v>7</v>
@@ -4039,22 +4106,22 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
         <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
@@ -4066,7 +4133,7 @@
         <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4081,7 +4148,7 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4270,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>22</v>
@@ -4212,7 +4279,7 @@
         <v>12</v>
       </c>
       <c r="AI21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ21" t="n">
         <v>14</v>
@@ -4236,22 +4303,22 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW21" t="n">
         <v>12</v>
@@ -4260,7 +4327,7 @@
         <v>23</v>
       </c>
       <c r="AY21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>8</v>
       </c>
       <c r="AE22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>4</v>
@@ -4391,7 +4458,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>9</v>
@@ -4403,7 +4470,7 @@
         <v>5</v>
       </c>
       <c r="AL22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM22" t="n">
         <v>20</v>
@@ -4421,19 +4488,19 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>16</v>
       </c>
       <c r="AV22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4640,7 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
@@ -4582,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
         <v>17</v>
@@ -4591,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="AN23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
         <v>26</v>
@@ -4606,13 +4673,13 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
@@ -4627,7 +4694,7 @@
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -4665,85 +4732,85 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="n">
         <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.325</v>
+        <v>0.333</v>
       </c>
       <c r="H24" t="n">
         <v>48.9</v>
       </c>
       <c r="I24" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J24" t="n">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.441</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M24" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
-        <v>0.317</v>
+        <v>0.322</v>
       </c>
       <c r="O24" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q24" t="n">
         <v>0.708</v>
       </c>
       <c r="R24" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="T24" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U24" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V24" t="n">
         <v>17.6</v>
       </c>
       <c r="W24" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X24" t="n">
         <v>4.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>101.3</v>
+        <v>101.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,10 +4822,10 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ24" t="n">
         <v>2</v>
@@ -4776,10 +4843,10 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4788,13 +4855,13 @@
         <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,7 +4870,7 @@
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4815,10 +4882,10 @@
         <v>16</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4955,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO25" t="n">
         <v>15</v>
@@ -4979,13 +5046,13 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775</v>
+        <v>0.769</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J26" t="n">
-        <v>88.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M26" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.827</v>
+        <v>0.823</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="U26" t="n">
         <v>24.6</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
         <v>5.6</v>
@@ -5095,31 +5162,31 @@
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>109.6</v>
+        <v>109.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5140,7 +5207,7 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5152,31 +5219,31 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="n">
         <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>15</v>
@@ -5319,7 +5386,7 @@
         <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
@@ -5361,7 +5428,7 @@
         <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5541,7 @@
         <v>8</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
@@ -5516,7 +5583,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
         <v>19</v>
@@ -5531,7 +5598,7 @@
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
@@ -5704,13 +5771,13 @@
         <v>18</v>
       </c>
       <c r="AU29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -5757,67 +5824,67 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" t="n">
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="J30" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.44</v>
+        <v>0.443</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.356</v>
+        <v>0.359</v>
       </c>
       <c r="O30" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P30" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R30" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S30" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
         <v>41.3</v>
       </c>
       <c r="U30" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y30" t="n">
         <v>5</v>
@@ -5826,13 +5893,13 @@
         <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,22 +5908,22 @@
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ30" t="n">
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5868,31 +5935,31 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP30" t="n">
         <v>22</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>21</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT30" t="n">
         <v>25</v>
       </c>
       <c r="AU30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5910,7 +5977,7 @@
         <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>0.487</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5957,10 +6024,10 @@
         <v>37.5</v>
       </c>
       <c r="J31" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L31" t="n">
         <v>7.9</v>
@@ -5975,55 +6042,55 @@
         <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.727</v>
+        <v>0.733</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U31" t="n">
         <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W31" t="n">
         <v>8.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
         <v>3.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB31" t="n">
         <v>98.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
@@ -6035,7 +6102,7 @@
         <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
         <v>16</v>
@@ -6047,19 +6114,19 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
       </c>
       <c r="AP31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>23</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>27</v>
-      </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>20</v>
@@ -6068,22 +6135,22 @@
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-18-2013-14</t>
+          <t>2014-01-18</t>
         </is>
       </c>
     </row>
